--- a/data/poi_sample_recommendations.xlsx
+++ b/data/poi_sample_recommendations.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,101 +413,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>poi_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Tên địa điểm</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>poi_type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>rating_filled</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>review_count</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>distance_km</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>keywords_clean</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>open_hours_clean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>maps_url</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>candidate_score</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>behavior_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>content_score</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>type_score</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>location_score</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>distance_score</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>quality_score</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>phd_score</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>fuzzy_score</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>type_context_score</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>contextual_score</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>fuzzy_h_score</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>topsis_score</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>final_score</t>
         </is>
@@ -528,1066 +531,1231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tháp Bà Ponagar</t>
+          <t>POI-05826</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Valley Viewpoint</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Khánh Hoà</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Tourist attraction</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4.5</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>32313</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>12.2653665</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>109.1953678</v>
+        <v>12.2274641</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>"tham quan" , "tháp" , "chụp ảnh" , "di tích" , "văn hóa"</t>
-        </is>
+        <v>108.7803661</v>
+      </c>
+      <c r="I2" t="n">
+        <v>45.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6 AM–6 PM</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Po+Nagar+Temple/@12.2653665,109.1927929,17z/data=!3m1!4b1!4m6!3m5!1s0x3170678c61b8f251:0x115f6f97f1af1d7c!8m2!3d12.2653665!4d109.1953678!16s%2Fm%2F02x5pgr?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.2606</v>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hanging+Valley+Viewpoint/@37.7210006,168.6323243,3z/data=!4m10!1m2!2m1!1sValley+Viewpoint!3m6!1s0x8096ed45986bde7b:0x50d0633f22ea65cd!8m2!3d37.7210006!4d-119.6489257!15sChBWYWxsZXkgVmlld3BvaW50WhIiEHZhbGxleSB2aWV3cG9pbnSSAQtzY2VuaWNfc3BvdJoBI0NoWkRTVWhOTUc5blMwVkpRMEZuU1VSeWNrcHhYMWxSRUFF4AEA-gEECAAQMA!16s%2Fg%2F11flp7b9kk?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.3329</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9754</v>
+        <v>0.3329</v>
       </c>
       <c r="P2" t="n">
-        <v>0.883</v>
+        <v>0.6228</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7141</v>
+        <v>0.105</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9617</v>
+        <v>0.5666</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8132</v>
+        <v>0.2872</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.7294</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.7294</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Làng nghề Trường Sơn</t>
+          <t>POI-05691</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Vườn Hoa Cẩm Tú Cầu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tourist attraction</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4.7</v>
+          <t>Lâm Đồng</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>1293</v>
+        <v>4.3</v>
       </c>
       <c r="F3" t="n">
-        <v>12.2135708</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>109.2005336</v>
+        <v>11.9488033</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>"tham quan" , "du lịch"</t>
-        </is>
+        <v>108.5052101</v>
+      </c>
+      <c r="I3" t="n">
+        <v>81.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7:30 AM–5 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/L%C3%A0ng+ngh%E1%BB%81+Tr%C6%B0%E1%BB%9Dng+S%C6%A1n+-+Tr%C6%B0%E1%BB%9Dng+S%C6%A1n+Craft+Village/@12.213557,109.1999237,17z/data=!3m1!4b1!4m6!3m5!1s0x31706745517ab043:0x6dcf164c392b42a3!8m2!3d12.213557!4d109.1999237!16s%2Fg%2F11ckky2c3y?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0813</v>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/V%C6%B0%E1%BB%9Dn+Hoa+C%E1%BA%A9m+T%C3%BA+C%E1%BA%A7u+M%E1%BB%9Bi/@11.9488033,108.5008327,17z/data=!4m10!1m2!2m1!1zVsaw4budbiBIb2EgQ-G6qW0gVMO6IEPhuqd1!3m6!1s0x317113fd11907be3:0xaf1e5b1a30c14b51!8m2!3d11.9488033!4d108.5052101!15sChtWxrDhu51uIEhvYSBD4bqpbSBUw7ogQ-G6p3VaHSIbdsaw4budbiBob2EgY-G6qW0gdMO6IGPhuqd1kgEJYXJib3JldHVtmgEjQ2haRFNVaE5NRzluUzBWSlEwRm5TVVJXTFRkcVprcFJFQUXgAQD6AQQIABAr!16s%2Fg%2F11fpr2slgz?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.3382</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9764</v>
+        <v>0.3382</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8157</v>
+        <v>0.3183</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6381</v>
+        <v>0.523</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9953</v>
+        <v>0.4538</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7809</v>
+        <v>0.2817</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4571</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chùa Suối Đổ</t>
+          <t>POI-05738</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Thác Ankroet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Buddhist temple</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4.6</v>
+          <t>Lâm Đồng</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tourist attraction</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>1127</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="n">
-        <v>12.2214957</v>
+        <v>140</v>
       </c>
       <c r="G4" t="n">
-        <v>109.1007854</v>
+        <v>11.9908823</v>
       </c>
       <c r="H4" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>"tâm linh" , "văn hóa" , "tham quan"</t>
-        </is>
+        <v>108.3669536</v>
+      </c>
+      <c r="I4" t="n">
+        <v>94.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6a | 9a | 12p | 3p | 6p | 9p | 12a | 3a</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Suoi+Do+Pagoda/@12.2215111,109.1008206,17z/data=!3m1!4b1!4m6!3m5!1s0x31705c0e9eaf2ba3:0xa36b08dbf256d5ca!8m2!3d12.2215111!4d109.1008206!16s%2Fg%2F11b779df9g?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1034</v>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Th%C3%A1c+Ankroet</t>
+        </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.3559</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9117</v>
+        <v>0.3559</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.2139</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6331</v>
+        <v>0.6823</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9657</v>
+        <v>0.7897</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7661</v>
+        <v>0.3767</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.4239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tong Lam Lo Son Temple</t>
+          <t>POI-01691</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>khu di tích lịch sử Lam Kinh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Buddhist temple</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4.7</v>
+          <t>Thanh Hoá</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>History museum</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>652</v>
+        <v>4.6</v>
       </c>
       <c r="F5" t="n">
-        <v>12.2829813</v>
+        <v>3005</v>
       </c>
       <c r="G5" t="n">
-        <v>109.1334343</v>
+        <v>19.9275606</v>
       </c>
       <c r="H5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>"tâm linh" , "văn hóa" , "tham quan"</t>
-        </is>
+        <v>105.4035142</v>
+      </c>
+      <c r="I5" t="n">
+        <v>946</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7:30 AM–5 PM</t>
+          <t>"tham quan" , "du lịch" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Tong+Lam+Lo+Son+Temple</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0892</v>
+          <t>6:30 AM–5:30 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/khu+di+t%C3%ADch+l%E1%BB%8Bch+s%E1%BB%AD+Lam+Kinh</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0.348</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9296</v>
+        <v>0.348</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7968</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.63</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0.967</v>
+        <v>0.8875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7648</v>
+        <v>0.3875</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.4944</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.3242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bảo tàng Hải dương học Nha Trang</t>
+          <t>POI-05813</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Great of Hai Van Mountains</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Museum</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4.2</v>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Historical landmark</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>2803</v>
+        <v>4.6</v>
       </c>
       <c r="F6" t="n">
-        <v>12.20825545</v>
+        <v>4121</v>
       </c>
       <c r="G6" t="n">
-        <v>109.21470715</v>
+        <v>16.1877377</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>"bảo tàng" , "văn hóa" , "tham quan"</t>
-        </is>
+        <v>108.1312942</v>
+      </c>
+      <c r="I6" t="n">
+        <v>453.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6 AM–6 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Museum+of+Oceanography/@12.2073287,109.2146547,17z/data=!3m1!4b1!4m6!3m5!1s0x3170673662ffffff:0x6cbdd6847bf4d318!8m2!3d12.2073287!4d109.2146547!16s%2Fg%2F121fqq6s?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.1774</v>
+          <t>7 AM–5:30 AM | 7 AM–5:30 PM | 7 AM–5 PM | 6a | 9a | 12p | 3p | 6p | 9p | 3a</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hai+Van+Pass/@16.1877377,108.1312942,17z/data=!3m1!4b1!4m6!3m5!1s0x3142219e02bc568b:0xb04a3eba486386b5!8m2!3d16.1877377!4d108.1312942!16s%2Fg%2F11p5lgqrq9?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.3785</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9673</v>
+        <v>0.3785</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7822</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6636</v>
+        <v>0.8369</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9101</v>
+        <v>0.8353</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7622</v>
+        <v>0.3762</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The Fairy Forest</t>
+          <t>POI-05987</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Headland and View of Hai Van Mountains</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tourist attraction</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4.8</v>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Historical landmark</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>4.6</v>
       </c>
       <c r="F7" t="n">
-        <v>12.1812182</v>
+        <v>4121</v>
       </c>
       <c r="G7" t="n">
-        <v>109.167098</v>
+        <v>16.1877377</v>
       </c>
       <c r="H7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>"tham quan" , "du lịch"</t>
-        </is>
+        <v>108.1312942</v>
+      </c>
+      <c r="I7" t="n">
+        <v>453.9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9 AM–10 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/The+Fairy+Forest/@42.2522329,-84.2137389,17z/data=!3m1!4b1!4m6!3m5!1s0x883cd76393bead6f:0x46e317c924ea3ee6!8m2!3d42.2522329!4d-84.2137389!16s%2Fg%2F11g9m5vkv1?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.1123</v>
+          <t>7 AM–5:30 AM | 7 AM–5:30 PM | 7 AM–5 PM | 6a | 9a | 12p | 3p | 6p | 9p | 3a</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hai+Van+Pass/@16.1877377,108.1312942,17z/data=!3m1!4b1!4m6!3m5!1s0x3142219e02bc568b:0xb04a3eba486386b5!8m2!3d16.1877377!4d108.1312942!16s%2Fg%2F11p5lgqrq9?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0.3613</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9403</v>
+        <v>0.3613</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7722</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6348</v>
+        <v>0.8369</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9122</v>
+        <v>0.8328</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7458</v>
+        <v>0.3756</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.3092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>view of waterfall from the top</t>
+          <t>POI-05812</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>View of the Bay and Sunken Ship</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tourist attraction</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4.5</v>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Historical landmark</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>4.8</v>
       </c>
       <c r="F8" t="n">
-        <v>12.2171834</v>
+        <v>140</v>
       </c>
       <c r="G8" t="n">
-        <v>109.1034564</v>
+        <v>16.1437541</v>
       </c>
       <c r="H8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
-        </is>
+        <v>108.2316063</v>
+      </c>
+      <c r="I8" t="n">
+        <v>446.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6a | 9a | 12p | 3p | 6p | 9p | 12a | 3a</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Th%C3%A1c+B%C3%ACnh+An+Waterfall/@12.2171834,109.1034564,17z/data=!3m1!4b1!4m6!3m5!1s0x31705dbbbacc3fc1:0x937b6634c87f64c0!8m2!3d12.2171834!4d109.1034564!16s%2Fg%2F11fjscgrqt?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2749</v>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/View+of+the+Bay+and+Sunken+Ship</t>
+        </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0.3671</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9132</v>
+        <v>0.3671</v>
       </c>
       <c r="P8" t="n">
-        <v>0.709</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.675</v>
+        <v>0.7153</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8253</v>
+        <v>0.8336</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7351</v>
+        <v>0.3515</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ĐAO HOA LAN</t>
+          <t>POI-06287</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>José Martí</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tourist attraction</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>4.2</v>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Heritage museum</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>2670</v>
+        <v>4.6</v>
       </c>
       <c r="F9" t="n">
-        <v>12.405657</v>
+        <v>572</v>
       </c>
       <c r="G9" t="n">
-        <v>109.2428447</v>
+        <v>21.0215133</v>
       </c>
       <c r="H9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>"tham quan" , "du lịch"</t>
-        </is>
+        <v>105.8577557</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1039.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6a | 9a | 12p | 3p | 6p | 9p | 12a | 3a</t>
+          <t>"nghệ thuật" , "chụp ảnh" , "tham quan" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hoa+Lan+Island+Resort/@12.405657,109.2428447,17z/data=!3m1!4b1!4m6!3m5!1s0x31706bb203d255a9:0x537363f2490120e!8m2!3d12.405657!4d109.2428447!16s%2Fg%2F122yyp31?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1395</v>
+          <t>9:30 AM–4 PM</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Jos%C3%A9+Mart%C3%AD+Memorial./@23.1227283,-82.4041596,15z/data=!4m10!1m2!2m1!1zSm9zw6kgTWFydMOt!3m6!1s0x88cd79e1bd4e654b:0x2f4cd3720557f2ad!8m2!3d23.1227283!4d-82.3866501!15sCgxKb3PDqSBNYXJ0w61aDiIMam9zw6kgbWFydMOtkgEPaGVyaXRhZ2VfbXVzZXVtmgEjQ2haRFNVaE5NRzluUzBWSlEwRm5TVU5hYVRsVGJrZDNFQUXgAQD6AQUI6QEQRQ!16s%2Fm%2F02q7crn?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.365</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8398</v>
+        <v>0.365</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7808</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.631</v>
+        <v>0.7821</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8047</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.3576</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.295</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Viewpoint of the Bay</t>
+          <t>POI-05817</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Graveyard and Mountain Viewpoint</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tourist attraction</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4.8</v>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Historical landmark</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>121</v>
+        <v>4.7</v>
       </c>
       <c r="F10" t="n">
-        <v>12.5867665</v>
+        <v>15</v>
       </c>
       <c r="G10" t="n">
-        <v>109.2417262</v>
+        <v>15.9164114</v>
       </c>
       <c r="H10" t="n">
-        <v>39</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
-        </is>
+        <v>107.6448154</v>
+      </c>
+      <c r="I10" t="n">
+        <v>441.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6a | 9a | 12p | 3p | 6p | 9p | 12a | 3a</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Kotor+Bay+Viewpoint/@42.424029,18.7826575,17z/data=!3m1!4b1!4m6!3m5!1s0x134c33001ab2fbd7:0xb014ea9f68cad44b!8m2!3d42.424029!4d18.7826575!16s%2Fg%2F11ld45b6mr?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2942</v>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Mountain+View+Cemetery/@37.8355133,-122.2325074,17z/data=!3m1!4b1!4m6!3m5!1s0x80857d006fa9edf5:0x8b1bd672f7382b2e!8m2!3d37.8355133!4d-122.2325074!16s%2Fg%2F11msbjks9m?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.3984</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.675</v>
+        <v>0.3984</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7612</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6565</v>
+        <v>0.6439</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8417</v>
+        <v>0.8383</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7305</v>
+        <v>0.3384</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.2935</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Đỉnh đèo Khánh Sơn</t>
+          <t>POI-05678</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Khe Lía</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Tuyên Quang</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Tourist attraction</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="E11" t="n">
-        <v>285</v>
+        <v>4.7</v>
       </c>
       <c r="F11" t="n">
-        <v>11.9722887</v>
+        <v>244</v>
       </c>
       <c r="G11" t="n">
-        <v>109.0058264</v>
+        <v>23.2941561</v>
       </c>
       <c r="H11" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan" , "tâm linh" , "văn hóa"</t>
-        </is>
+        <v>105.3108231</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1296.1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6a | 9a | 12p | 3p | 6p | 9p | 3a | 12a</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/%C4%90%E1%BB%89nh+%C4%91%C3%A8o+Kh%C3%A1nh+S%C6%A1n/@11.9719015,109.0052971,17z/data=!3m1!4b1!4m6!3m5!1s0x3170f1358f342c33:0x45e3bc08ea70b58a!8m2!3d11.9719015!4d109.0052971!16s%2Fg%2F11h7_r2513?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2588</v>
+          <t>6a | 9a | 12p | 3p | 6p | 3a | 9p | 12a</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Khe+Lia+Panorama/@23.2941827,105.3107136,17z/data=!3m1!4b1!4m6!3m5!1s0x36cbe39eb8ed465f:0x148f5798a62d006!8m2!3d23.2941827!4d105.3107136!16s%2Fg%2F11hf9t_tv4?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.3255</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6985</v>
+        <v>0.3255</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7519</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.7696</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8508</v>
+        <v>0.8051</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7278</v>
+        <v>0.3552</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bãi dài nha trang</t>
+          <t>POI-01447</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Di tích Minh Đạm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Beach</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4.5</v>
+          <t>Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Local history museum</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>837</v>
+        <v>4.4</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0270699</v>
+        <v>2250</v>
       </c>
       <c r="G12" t="n">
-        <v>109.224571</v>
+        <v>10.4057242</v>
       </c>
       <c r="H12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>"nghệ thuật" , "chụp ảnh" , "tham quan" , "biển" , "nghỉ dưỡng"</t>
-        </is>
+        <v>107.2610718</v>
+      </c>
+      <c r="I12" t="n">
+        <v>293.4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Không rõ</t>
+          <t>"tham quan" , "du lịch" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bai+Dai/@12.0270699,109.224571,13z/data=!3m1!4b1!4m6!3m5!1s0x31708b2043a6ae31:0xd3ff083871c7e4fe!8m2!3d12.0270699!4d109.224571!16s%2Fg%2F1q5bmvqwt?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.1855</v>
+          <t>7 AM–6 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Di+t%C3%ADch+Minh+%C4%90%E1%BA%A1m</t>
+        </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0.3489</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8022</v>
+        <v>0.3489</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7317</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.7981</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8692</v>
+        <v>0.7773</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7266</v>
+        <v>0.354</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2877</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VinWonders Nha Trang</t>
+          <t>POI-05659</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Cầu Koi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Theme park</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4.6</v>
+          <t>Quảng Ninh</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tourist attraction</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>19532</v>
+        <v>4.4</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2170491</v>
+        <v>111</v>
       </c>
       <c r="G13" t="n">
-        <v>109.2408716</v>
+        <v>20.9558791</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>"công viên" , "vui chơi" , "giải trí" , "chụp ảnh" , "tham quan" , "dã ngoại" , "chợ" , "văn hóa" , "trải nghiệm"</t>
-        </is>
+        <v>107.0727478</v>
+      </c>
+      <c r="I13" t="n">
+        <v>995.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>Không rõ</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/place/VinWonders+Nha+Trang/@12.2170491,109.2382967,17z/data=!3m1!4b1!4m6!3m5!1s0x317067c7c4267451:0x826b650efe77e523!8m2!3d12.2170491!4d109.2408716!16s%2Fg%2F11h52s0zxz?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1644</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/C%E1%BA%A7u+Koi</t>
+        </is>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
+        <v>0.3831</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9552</v>
+        <v>0.3831</v>
       </c>
       <c r="P13" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5918</v>
+        <v>0.6649</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9244</v>
+        <v>0.8154</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7248</v>
+        <v>0.3368</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2871</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chùa Đa Bảo</t>
+          <t>POI-06294</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Di tích Khởi nghĩa Bắc Sơn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Buddhist temple</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4.5</v>
+          <t>Lạng Sơn</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>War museum</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>628</v>
+        <v>4.4</v>
       </c>
       <c r="F14" t="n">
-        <v>12.3048873</v>
+        <v>199</v>
       </c>
       <c r="G14" t="n">
-        <v>109.2178696</v>
+        <v>21.9283071</v>
       </c>
       <c r="H14" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>"tâm linh" , "văn hóa" , "tham quan"</t>
-        </is>
+        <v>106.3500417</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1119</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Không rõ</t>
+          <t>"nghệ thuật" , "chụp ảnh" , "tham quan" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Ch%C3%B9a+%C4%90a+B%E1%BA%A3o/@11.5354449,107.9307984,9z/data=!4m10!1m2!2m1!1zQ2jDuWEgxJBhIELhuqNv!3m6!1s0x3170692d8505d587:0x78e943ca952608ab!8m2!3d12.3049331!4d109.2179144!15sCg9DaMO5YSDEkGEgQuG6o29aESIPY2jDuWEgxJFhIGLhuqNvkgEPYnVkZGhpc3RfdGVtcGxlmgFEQ2k5RFFVbFJRVU52WkVOb2RIbGpSamx2VDJ3NVJGZEdPVWhUYkZZMVRYcFdSMUV3Wkc5Vk0wcFpZVWhuZDFOdVl4QULgAQD6AQUImgEQNw!16s%2Fg%2F11sh45npbc?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>0.1189</v>
+          <t>8 AM–5 PM</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Di+t%C3%ADch+Kh%E1%BB%9Fi+ngh%C4%A9a+B%E1%BA%AFc+S%C6%A1n</t>
+        </is>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.3738</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9358</v>
+        <v>0.3738</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6737</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6167</v>
+        <v>0.7309</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8832</v>
+        <v>0.7924</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.3443</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.2858</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bãi Dài Cam Ranh</t>
+          <t>POI-00675</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Cang Bac Mê</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Beach</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>4.8</v>
+          <t>Tuyên Quang</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Historical landmark</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>837</v>
+        <v>4.4</v>
       </c>
       <c r="F15" t="n">
-        <v>12.0270699</v>
+        <v>145</v>
       </c>
       <c r="G15" t="n">
-        <v>109.224571</v>
+        <v>22.7297296</v>
       </c>
       <c r="H15" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>"biển" , "vui chơi" , "chụp ảnh" , "nghĩ dưỡng" , "nghỉ dưỡng"</t>
-        </is>
+        <v>105.3741674</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1234.7</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>"bảo tàng" , "văn hóa" , "tham quan" , "di tích" , "lịch sử"</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>Không rõ</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/place/Bai+Dai/@12.0270669,109.1833714,13z/data=!3m1!4b1!4m6!3m5!1s0x31708b2043a6ae31:0xd3ff083871c7e4fe!8m2!3d12.0270699!4d109.224571!16s%2Fg%2F1q5bmvqwt?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0.0786</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Di+t%C3%ADch+C%C4%83ng+B%E1%BA%AFc+M%C3%AA/@22.7308573,105.3745508,17z/data=!3m1!4b1!4m6!3m5!1s0x36cb98cc8b8c1ce9:0xa86a2cc1c4cff988!8m2!3d22.7308573!4d105.3745508!16s%2Fg%2F11hck1nqng?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0.3249</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8022</v>
+        <v>0.3249</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7647</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6008</v>
+        <v>0.6722</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9026</v>
+        <v>0.805</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7215</v>
+        <v>0.3357</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.283</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Trại Sim</t>
+          <t>POI-05063</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Khánh Hoà</t>
+          <t>Archeological Excavations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tourist attraction</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>4.9</v>
+          <t>Thái Nguyên</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Heritage museum</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>4.7</v>
       </c>
       <c r="F16" t="n">
-        <v>12.3291587</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>109.1236122</v>
+        <v>21.7953663</v>
       </c>
       <c r="H16" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>"tham quan" , "du lịch"</t>
-        </is>
+        <v>105.8865928</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1119.2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6a | 9a | 12p | 3p | 6p | 9p | 12a | 3a</t>
+          <t>"tham quan" , "du lịch" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Tr%E1%BA%A1i+Sim/@12.3292367,109.1235543,17z/data=!3m1!4b1!4m6!3m5!1s0x31706713369e6063:0x8666810373ac5aa6!8m2!3d12.3292367!4d109.1235543!16s%2Fg%2F11wfkztvz8?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0.1741</v>
+          <t>Không rõ</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/Archeological+Excavations</t>
+        </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0.3327</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8933</v>
+        <v>0.3327</v>
       </c>
       <c r="P16" t="n">
-        <v>0.742</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6433</v>
+        <v>0.6309</v>
       </c>
       <c r="R16" t="n">
-        <v>0.837</v>
+        <v>0.8061</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7208</v>
+        <v>0.3277</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2794</v>
       </c>
     </row>
   </sheetData>

--- a/data/poi_sample_recommendations.xlsx
+++ b/data/poi_sample_recommendations.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,112 +429,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>poi_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Tên địa điểm</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>poi_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>rating_filled</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>review_count</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>distance_km</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>keywords_clean</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>open_hours_clean</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>maps_url</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>candidate_score</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>behavior_score</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>content_score</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>distance_score</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>quality_score</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>type_context_score</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>contextual_score</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fuzzy_h_score</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>topsis_score</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>final_score</t>
         </is>
@@ -595,30 +607,30 @@
         <v>0.105</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5666</v>
+        <v>0.3959</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2872</v>
+        <v>0.2445</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3284</v>
+        <v>0.2752</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7294</v>
+        <v>0.6382</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7294</v>
+        <v>0.6382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POI-05691</t>
+          <t>POI-05738</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vườn Hoa Cẩm Tú Cầu</t>
+          <t>Thác Ankroet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -628,23 +640,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tourist attraction</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="G3" t="n">
-        <v>11.9488033</v>
+        <v>11.9908823</v>
       </c>
       <c r="H3" t="n">
-        <v>108.5052101</v>
+        <v>108.3669536</v>
       </c>
       <c r="I3" t="n">
-        <v>81.8</v>
+        <v>94.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -658,213 +670,213 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/V%C6%B0%E1%BB%9Dn+Hoa+C%E1%BA%A9m+T%C3%BA+C%E1%BA%A7u+M%E1%BB%9Bi/@11.9488033,108.5008327,17z/data=!4m10!1m2!2m1!1zVsaw4budbiBIb2EgQ-G6qW0gVMO6IEPhuqd1!3m6!1s0x317113fd11907be3:0xaf1e5b1a30c14b51!8m2!3d11.9488033!4d108.5052101!15sChtWxrDhu51uIEhvYSBD4bqpbSBUw7ogQ-G6p3VaHSIbdsaw4budbiBob2EgY-G6qW0gdMO6IGPhuqd1kgEJYXJib3JldHVtmgEjQ2haRFNVaE5NRzluUzBWSlEwRm5TVVJXTFRkcVprcFJFQUXgAQD6AQQIABAr!16s%2Fg%2F11fpr2slgz?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/search/Th%C3%A1c+Ankroet</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.3382</v>
+        <v>0.3559</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3382</v>
+        <v>0.3559</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3183</v>
+        <v>0.2139</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.523</v>
+        <v>0.6823</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4538</v>
+        <v>0.7709</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2817</v>
+        <v>0.372</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3348</v>
+        <v>0.4532</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4571</v>
+        <v>0.5226</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4571</v>
+        <v>0.5226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>POI-05738</t>
+          <t>POI-01691</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thác Ankroet</t>
+          <t>khu di tích lịch sử Lam Kinh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lâm Đồng</t>
+          <t>Thanh Hoá</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tourist attraction</t>
+          <t>History museum</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F4" t="n">
-        <v>140</v>
+        <v>3005</v>
       </c>
       <c r="G4" t="n">
-        <v>11.9908823</v>
+        <v>19.9275606</v>
       </c>
       <c r="H4" t="n">
-        <v>108.3669536</v>
+        <v>105.4035142</v>
       </c>
       <c r="I4" t="n">
-        <v>94.3</v>
+        <v>946</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
+          <t>"tham quan" , "du lịch" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Không rõ</t>
+          <t>6:30 AM–5:30 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Th%C3%A1c+Ankroet</t>
+          <t>https://www.google.com/maps/search/khu+di+t%C3%ADch+l%E1%BB%8Bch+s%E1%BB%AD+Lam+Kinh</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.3559</v>
+        <v>0.348</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3559</v>
+        <v>0.348</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2139</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6823</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7897</v>
+        <v>0.8722</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3767</v>
+        <v>0.3837</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4591</v>
+        <v>0.4896</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4239</v>
+        <v>0.4454</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4239</v>
+        <v>0.4454</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POI-01691</t>
+          <t>POI-05813</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>khu di tích lịch sử Lam Kinh</t>
+          <t>Great of Hai Van Mountains</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thanh Hoá</t>
+          <t>Đà Nẵng</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>History museum</t>
+          <t>Historical landmark</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>4.6</v>
       </c>
       <c r="F5" t="n">
-        <v>3005</v>
+        <v>4121</v>
       </c>
       <c r="G5" t="n">
-        <v>19.9275606</v>
+        <v>16.1877377</v>
       </c>
       <c r="H5" t="n">
-        <v>105.4035142</v>
+        <v>108.1312942</v>
       </c>
       <c r="I5" t="n">
-        <v>946</v>
+        <v>453.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>"tham quan" , "du lịch" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6:30 AM–5:30 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
+          <t>7 AM–5:30 AM | 7 AM–5:30 PM | 7 AM–5 PM | 6a | 9a | 12p | 3p | 6p | 9p | 3a</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/khu+di+t%C3%ADch+l%E1%BB%8Bch+s%E1%BB%AD+Lam+Kinh</t>
+          <t>https://www.google.com/maps/place/Hai+Van+Pass/@16.1877377,108.1312942,17z/data=!3m1!4b1!4m6!3m5!1s0x3142219e02bc568b:0xb04a3eba486386b5!8m2!3d16.1877377!4d108.1312942!16s%2Fg%2F11p5lgqrq9?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.348</v>
+        <v>0.3785</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.348</v>
+        <v>0.3785</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8369</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8875</v>
+        <v>0.8118</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3875</v>
+        <v>0.3703</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4944</v>
+        <v>0.4771</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3242</v>
+        <v>0.4264</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3242</v>
+        <v>0.4264</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POI-05813</t>
+          <t>POI-05987</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Great of Hai Van Mountains</t>
+          <t>Headland and View of Hai Van Mountains</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -908,13 +920,13 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.3785</v>
+        <v>0.3613</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3785</v>
+        <v>0.3613</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -923,30 +935,30 @@
         <v>0.8369</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8353</v>
+        <v>0.8092</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3762</v>
+        <v>0.3697</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4845</v>
+        <v>0.4735</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3104</v>
+        <v>0.4252</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3104</v>
+        <v>0.4252</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>POI-05987</t>
+          <t>POI-05812</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Headland and View of Hai Van Mountains</t>
+          <t>View of the Bay and Sunken Ship</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -960,19 +972,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="F7" t="n">
-        <v>4121</v>
+        <v>140</v>
       </c>
       <c r="G7" t="n">
-        <v>16.1877377</v>
+        <v>16.1437541</v>
       </c>
       <c r="H7" t="n">
-        <v>108.1312942</v>
+        <v>108.2316063</v>
       </c>
       <c r="I7" t="n">
-        <v>453.9</v>
+        <v>446.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -981,54 +993,54 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7 AM–5:30 AM | 7 AM–5:30 PM | 7 AM–5 PM | 6a | 9a | 12p | 3p | 6p | 9p | 3a</t>
+          <t>Không rõ</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hai+Van+Pass/@16.1877377,108.1312942,17z/data=!3m1!4b1!4m6!3m5!1s0x3142219e02bc568b:0xb04a3eba486386b5!8m2!3d16.1877377!4d108.1312942!16s%2Fg%2F11p5lgqrq9?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/search/View+of+the+Bay+and+Sunken+Ship</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.3613</v>
+        <v>0.3671</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3613</v>
+        <v>0.3671</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8369</v>
+        <v>0.7153</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8328</v>
+        <v>0.8101</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3756</v>
+        <v>0.3456</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4809</v>
+        <v>0.4548</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3092</v>
+        <v>0.4206</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3092</v>
+        <v>0.4206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POI-05812</t>
+          <t>POI-05817</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>View of the Bay and Sunken Ship</t>
+          <t>Graveyard and Mountain Viewpoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,19 +1054,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F8" t="n">
-        <v>140</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>16.1437541</v>
+        <v>15.9164114</v>
       </c>
       <c r="H8" t="n">
-        <v>108.2316063</v>
+        <v>107.6448154</v>
       </c>
       <c r="I8" t="n">
-        <v>446.5</v>
+        <v>441.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1068,38 +1080,38 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/View+of+the+Bay+and+Sunken+Ship</t>
+          <t>https://www.google.com/maps/place/Mountain+View+Cemetery/@37.8355133,-122.2325074,17z/data=!3m1!4b1!4m6!3m5!1s0x80857d006fa9edf5:0x8b1bd672f7382b2e!8m2!3d37.8355133!4d-122.2325074!16s%2Fg%2F11msbjks9m?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3671</v>
+        <v>0.3984</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3671</v>
+        <v>0.3984</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7153</v>
+        <v>0.6439</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8336</v>
+        <v>0.8148</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3515</v>
+        <v>0.3325</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4621</v>
+        <v>0.4496</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2976</v>
+        <v>0.4201</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2976</v>
+        <v>0.4201</v>
       </c>
     </row>
     <row r="9">
@@ -1169,35 +1181,35 @@
         <v>0.7821</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8047</v>
+        <v>0.7872</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3576</v>
+        <v>0.3532</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4638</v>
+        <v>0.4583</v>
       </c>
       <c r="U9" t="n">
-        <v>0.295</v>
+        <v>0.4151</v>
       </c>
       <c r="V9" t="n">
-        <v>0.295</v>
+        <v>0.4151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POI-05817</t>
+          <t>POI-06597</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Graveyard and Mountain Viewpoint</t>
+          <t>Stonehenge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Đà Nẵng</t>
+          <t>Lâm Đồng</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1206,64 +1218,64 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>15.9164114</v>
+        <v>11.6070614</v>
       </c>
       <c r="H10" t="n">
-        <v>107.6448154</v>
+        <v>108.349538</v>
       </c>
       <c r="I10" t="n">
-        <v>441.8</v>
+        <v>115.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan" , "di tích" , "lịch sử"</t>
+          <t>"nghệ thuật" , "chụp ảnh" , "tham quan" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Không rõ</t>
+          <t> Closed · Opens 9:30 AM Mon See more hours  | 6a | 9a | 12p | 3p | 6p | 9p</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mountain+View+Cemetery/@37.8355133,-122.2325074,17z/data=!3m1!4b1!4m6!3m5!1s0x80857d006fa9edf5:0x8b1bd672f7382b2e!8m2!3d37.8355133!4d-122.2325074!16s%2Fg%2F11msbjks9m?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Stonehenge/@51.178882,-1.826215,17z/data=!3m1!4b1!4m6!3m5!1s0x4873e63b850af611:0x979170e2bcd3d2dd!8m2!3d51.178882!4d-1.826215!16zL20vMDZ3Zmc?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.3984</v>
+        <v>0.3237</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3984</v>
+        <v>0.3237</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.0343</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6439</v>
+        <v>0.6005</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8383</v>
+        <v>0.7661</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3384</v>
+        <v>0.3185</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4569</v>
+        <v>0.4176</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2935</v>
+        <v>0.4095</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2935</v>
+        <v>0.4095</v>
       </c>
     </row>
     <row r="11">
@@ -1333,142 +1345,142 @@
         <v>0.7696</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8051</v>
+        <v>0.7738</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3552</v>
+        <v>0.3474</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4554</v>
+        <v>0.4456</v>
       </c>
       <c r="U11" t="n">
-        <v>0.293</v>
+        <v>0.409</v>
       </c>
       <c r="V11" t="n">
-        <v>0.293</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>POI-01447</t>
+          <t>POI-06294</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Di tích Minh Đạm</t>
+          <t>Di tích Khởi nghĩa Bắc Sơn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hồ Chí Minh</t>
+          <t>Lạng Sơn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Local history museum</t>
+          <t>War museum</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>4.4</v>
       </c>
       <c r="F12" t="n">
-        <v>2250</v>
+        <v>199</v>
       </c>
       <c r="G12" t="n">
-        <v>10.4057242</v>
+        <v>21.9283071</v>
       </c>
       <c r="H12" t="n">
-        <v>107.2610718</v>
+        <v>106.3500417</v>
       </c>
       <c r="I12" t="n">
-        <v>293.4</v>
+        <v>1119</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>"tham quan" , "du lịch" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
+          <t>"nghệ thuật" , "chụp ảnh" , "tham quan" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7 AM–6 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
+          <t>8 AM–5 PM</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Di+t%C3%ADch+Minh+%C4%90%E1%BA%A1m</t>
+          <t>https://www.google.com/maps/search/Di+t%C3%ADch+Kh%E1%BB%9Fi+ngh%C4%A9a+B%E1%BA%AFc+S%C6%A1n</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.3489</v>
+        <v>0.3738</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3489</v>
+        <v>0.3738</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7981</v>
+        <v>0.7309</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7773</v>
+        <v>0.7736</v>
       </c>
       <c r="S12" t="n">
-        <v>0.354</v>
+        <v>0.3396</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4552</v>
+        <v>0.447</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2877</v>
+        <v>0.408</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2877</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>POI-05659</t>
+          <t>POI-00675</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cầu Koi</t>
+          <t>Cang Bac Mê</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Quảng Ninh</t>
+          <t>Tuyên Quang</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tourist attraction</t>
+          <t>Historical landmark</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>4.4</v>
       </c>
       <c r="F13" t="n">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="G13" t="n">
-        <v>20.9558791</v>
+        <v>22.7297296</v>
       </c>
       <c r="H13" t="n">
-        <v>107.0727478</v>
+        <v>105.3741674</v>
       </c>
       <c r="I13" t="n">
-        <v>995.3</v>
+        <v>1234.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
+          <t>"bảo tàng" , "văn hóa" , "tham quan" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1478,239 +1490,239 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/C%E1%BA%A7u+Koi</t>
+          <t>https://www.google.com/maps/place/Di+t%C3%ADch+C%C4%83ng+B%E1%BA%AFc+M%C3%AA/@22.7308573,105.3745508,17z/data=!3m1!4b1!4m6!3m5!1s0x36cb98cc8b8c1ce9:0xa86a2cc1c4cff988!8m2!3d22.7308573!4d105.3745508!16s%2Fg%2F11hck1nqng?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.3831</v>
+        <v>0.3249</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3831</v>
+        <v>0.3249</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6649</v>
+        <v>0.6722</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8154</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3368</v>
+        <v>0.3279</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4507</v>
+        <v>0.4295</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2871</v>
+        <v>0.4047</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2871</v>
+        <v>0.4047</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POI-06294</t>
+          <t>POI-05063</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Di tích Khởi nghĩa Bắc Sơn</t>
+          <t>Archeological Excavations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lạng Sơn</t>
+          <t>Thái Nguyên</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>War museum</t>
+          <t>Heritage museum</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F14" t="n">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>21.9283071</v>
+        <v>21.7953663</v>
       </c>
       <c r="H14" t="n">
-        <v>106.3500417</v>
+        <v>105.8865928</v>
       </c>
       <c r="I14" t="n">
-        <v>1119</v>
+        <v>1119.2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>"nghệ thuật" , "chụp ảnh" , "tham quan" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
+          <t>"tham quan" , "du lịch" , "bảo tàng" , "văn hóa" , "di tích" , "lịch sử"</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8 AM–5 PM</t>
+          <t>Không rõ</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Di+t%C3%ADch+Kh%E1%BB%9Fi+ngh%C4%A9a+B%E1%BA%AFc+S%C6%A1n</t>
+          <t>https://www.google.com/maps/search/Archeological+Excavations</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3738</v>
+        <v>0.3327</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3738</v>
+        <v>0.3327</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7309</v>
+        <v>0.6309</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7924</v>
+        <v>0.7749</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3443</v>
+        <v>0.3199</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4529</v>
+        <v>0.4243</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2858</v>
+        <v>0.4035</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2858</v>
+        <v>0.4035</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>POI-00675</t>
+          <t>POI-06078</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cang Bac Mê</t>
+          <t>Awesome Viewpoint</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuyên Quang</t>
+          <t>Quảng Trị</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Historical landmark</t>
+          <t>Tourist attraction</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>22.7297296</v>
+        <v>16.8841892</v>
       </c>
       <c r="H15" t="n">
-        <v>105.3741674</v>
+        <v>106.569474</v>
       </c>
       <c r="I15" t="n">
-        <v>1234.7</v>
+        <v>588.8</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>"bảo tàng" , "văn hóa" , "tham quan" , "di tích" , "lịch sử"</t>
+          <t>"ngắm cảnh" , "chụp ảnh" , "tham quan"</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Không rõ</t>
+          <t>6a | 9a | 12p | 3p | 6p | 9p | 12a | 3a</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Di+t%C3%ADch+C%C4%83ng+B%E1%BA%AFc+M%C3%AA/@22.7308573,105.3745508,17z/data=!3m1!4b1!4m6!3m5!1s0x36cb98cc8b8c1ce9:0xa86a2cc1c4cff988!8m2!3d22.7308573!4d105.3745508!16s%2Fg%2F11hck1nqng?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Awesome+Viewpoint/@11.5216075,100.7249425,5z/data=!4m10!1m2!2m1!1sAwesome+Viewpoint!3m6!1s0x3391c9002391e3fd:0xf6bb217cfefeba2e!8m2!3d16.656852!4d120.788092!15sChFBd2Vzb21lIFZpZXdwb2ludJIBEnRvdXJpc3RfYXR0cmFjdGlvbuABAA!16s%2Fg%2F11xlglg0ty?entry=ttu&amp;g_ep=EgoyMDI2MDkwOS4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3249</v>
+        <v>0.3497</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3249</v>
+        <v>0.3497</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6722</v>
+        <v>0.6692</v>
       </c>
       <c r="R15" t="n">
-        <v>0.805</v>
+        <v>0.7625</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3357</v>
+        <v>0.3245</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4393</v>
+        <v>0.4295</v>
       </c>
       <c r="U15" t="n">
-        <v>0.283</v>
+        <v>0.4005</v>
       </c>
       <c r="V15" t="n">
-        <v>0.283</v>
+        <v>0.4005</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>POI-05063</t>
+          <t>POI-01447</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Archeological Excavations</t>
+          <t>Di tích Minh Đạm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thái Nguyên</t>
+          <t>Hồ Chí Minh</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Heritage museum</t>
+          <t>Local history museum</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>2250</v>
       </c>
       <c r="G16" t="n">
-        <v>21.7953663</v>
+        <v>10.4057242</v>
       </c>
       <c r="H16" t="n">
-        <v>105.8865928</v>
+        <v>107.2610718</v>
       </c>
       <c r="I16" t="n">
-        <v>1119.2</v>
+        <v>293.4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1719,43 +1731,43 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Không rõ</t>
+          <t>7 AM–6 PM | 6a | 9a | 12p | 3p | 6p | 9p</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Archeological+Excavations</t>
+          <t>https://www.google.com/maps/search/Di+t%C3%ADch+Minh+%C4%90%E1%BA%A1m</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.3327</v>
+        <v>0.3489</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3327</v>
+        <v>0.3489</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6309</v>
+        <v>0.7981</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8061</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3277</v>
+        <v>0.3415</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4341</v>
+        <v>0.4396</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2794</v>
+        <v>0.3928</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2794</v>
+        <v>0.3928</v>
       </c>
     </row>
   </sheetData>
